--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131155584</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,6 +775,128 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Fågelinventering Hålsberget 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131155728</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>V om Hålen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574242</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6696507</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Entita och talltita samtidigt.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Albin Kozma</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>

--- a/artfynd/A 29792-2025 artfynd.xlsx
+++ b/artfynd/A 29792-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,8 +911,17 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>